--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.00765943719771</v>
+        <v>1.626244658544629</v>
       </c>
       <c r="D2" t="n">
-        <v>10.03975737157701</v>
+        <v>1.631460572881265</v>
       </c>
       <c r="E2" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F2" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.79746285447287</v>
+        <v>5.004587713851842</v>
       </c>
       <c r="D3" t="n">
-        <v>30.67359136141543</v>
+        <v>4.984458596230008</v>
       </c>
       <c r="E3" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F3" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.569552636010224</v>
+        <v>1.230052303351661</v>
       </c>
       <c r="D4" t="n">
-        <v>7.29480492583683</v>
+        <v>1.185405800448485</v>
       </c>
       <c r="E4" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F4" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.39313960623041</v>
+        <v>1.688885186012442</v>
       </c>
       <c r="D5" t="n">
-        <v>10.36787936339962</v>
+        <v>1.684780396552439</v>
       </c>
       <c r="E5" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F5" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.60869166957373</v>
+        <v>5.623912396305731</v>
       </c>
       <c r="D6" t="n">
-        <v>34.37796453989722</v>
+        <v>5.586419237733298</v>
       </c>
       <c r="E6" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F6" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.37974998243408</v>
+        <v>3.149209372145538</v>
       </c>
       <c r="D7" t="n">
-        <v>19.12907807401874</v>
+        <v>3.108475187028044</v>
       </c>
       <c r="E7" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F7" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.7248251952098</v>
+        <v>6.292784094221593</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7196613134377</v>
+        <v>6.291944963433626</v>
       </c>
       <c r="E8" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F8" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.03678533822061</v>
+        <v>3.255977617460849</v>
       </c>
       <c r="D9" t="n">
-        <v>19.75859879812996</v>
+        <v>3.210772304696119</v>
       </c>
       <c r="E9" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F9" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.64223115904045</v>
+        <v>3.841862563344073</v>
       </c>
       <c r="D10" t="n">
-        <v>23.50564554384905</v>
+        <v>3.81966740087547</v>
       </c>
       <c r="E10" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F10" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.12165915370896</v>
+        <v>4.894769612477706</v>
       </c>
       <c r="D11" t="n">
-        <v>29.64176241923866</v>
+        <v>4.816786393126282</v>
       </c>
       <c r="E11" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F11" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.85997559874819</v>
+        <v>1.764746034796582</v>
       </c>
       <c r="D12" t="n">
-        <v>10.43506164163473</v>
+        <v>1.695697516765643</v>
       </c>
       <c r="E12" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F12" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.40344122999091</v>
+        <v>3.478059199873523</v>
       </c>
       <c r="D13" t="n">
-        <v>15.71391237619774</v>
+        <v>2.553510761132133</v>
       </c>
       <c r="E13" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F13" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.68275426763407</v>
+        <v>2.385947568490536</v>
       </c>
       <c r="D14" t="n">
-        <v>15.08227723218554</v>
+        <v>2.450870050230149</v>
       </c>
       <c r="E14" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F14" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.95347632636852</v>
+        <v>2.754939903034885</v>
       </c>
       <c r="D15" t="n">
-        <v>16.24736485112748</v>
+        <v>2.640196788308216</v>
       </c>
       <c r="E15" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F15" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.7060819913826</v>
+        <v>1.577238323599673</v>
       </c>
       <c r="D16" t="n">
-        <v>10.23120115451557</v>
+        <v>1.66257018760878</v>
       </c>
       <c r="E16" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F16" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>9.540723724513622</v>
+        <v>1.550367605233464</v>
       </c>
       <c r="D17" t="n">
-        <v>8.611439013824796</v>
+        <v>1.39935883974653</v>
       </c>
       <c r="E17" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F17" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17.43979025054592</v>
+        <v>2.833965915713712</v>
       </c>
       <c r="D18" t="n">
-        <v>17.9537387839809</v>
+        <v>2.917482552396895</v>
       </c>
       <c r="E18" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F18" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24.19159398853644</v>
+        <v>3.931134023137171</v>
       </c>
       <c r="D19" t="n">
-        <v>11.31510731227835</v>
+        <v>1.838704938245232</v>
       </c>
       <c r="E19" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F19" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>30.42837649764394</v>
+        <v>4.94461118086714</v>
       </c>
       <c r="D20" t="n">
-        <v>6.103277807866851</v>
+        <v>0.9917826437783633</v>
       </c>
       <c r="E20" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F20" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>29.31435610314211</v>
+        <v>4.763582866760593</v>
       </c>
       <c r="D21" t="n">
-        <v>25.51960031034969</v>
+        <v>4.146935050431825</v>
       </c>
       <c r="E21" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F21" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>21.86829262247563</v>
+        <v>3.55359755115229</v>
       </c>
       <c r="D22" t="n">
-        <v>24.97260308837852</v>
+        <v>4.05804800186151</v>
       </c>
       <c r="E22" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F22" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>34.94833880159143</v>
+        <v>5.679105055258608</v>
       </c>
       <c r="D23" t="n">
-        <v>22.59493695295224</v>
+        <v>3.671677254854739</v>
       </c>
       <c r="E23" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F23" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>25.21903813257807</v>
+        <v>4.098093696543938</v>
       </c>
       <c r="D24" t="n">
-        <v>16.69784340224579</v>
+        <v>2.71339955286494</v>
       </c>
       <c r="E24" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F24" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>28.98723857148176</v>
+        <v>4.710426267865787</v>
       </c>
       <c r="D25" t="n">
-        <v>18.87769837561833</v>
+        <v>3.067625986037979</v>
       </c>
       <c r="E25" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F25" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>24.43819051506245</v>
+        <v>3.971205958697648</v>
       </c>
       <c r="D26" t="n">
-        <v>12.74009906570384</v>
+        <v>2.070266098176874</v>
       </c>
       <c r="E26" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F26" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>37.26001676835352</v>
+        <v>6.054752724857448</v>
       </c>
       <c r="D27" t="n">
-        <v>14.83055335133943</v>
+        <v>2.409964919592657</v>
       </c>
       <c r="E27" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F27" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>18.64773295192388</v>
+        <v>3.03025660468763</v>
       </c>
       <c r="D28" t="n">
-        <v>13.15829973792731</v>
+        <v>2.138223707413188</v>
       </c>
       <c r="E28" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F28" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>27.68049855042355</v>
+        <v>4.498081014443827</v>
       </c>
       <c r="D29" t="n">
-        <v>3.914103223632643</v>
+        <v>0.6360417738403046</v>
       </c>
       <c r="E29" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F29" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>9.937023079844252</v>
+        <v>1.614766250474691</v>
       </c>
       <c r="D30" t="n">
-        <v>14.81025870496155</v>
+        <v>2.406667039556252</v>
       </c>
       <c r="E30" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F30" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>1.656505116868224</v>
+        <v>0.2691820814910864</v>
       </c>
       <c r="D31" t="n">
-        <v>5.294670962644313</v>
+        <v>0.8603840314297009</v>
       </c>
       <c r="E31" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F31" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>20.02023975880409</v>
+        <v>3.253288960805664</v>
       </c>
       <c r="D32" t="n">
-        <v>10.8605078228553</v>
+        <v>1.764832521213986</v>
       </c>
       <c r="E32" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F32" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>12.41974234837422</v>
+        <v>2.018208131610811</v>
       </c>
       <c r="D33" t="n">
-        <v>18.47839392028495</v>
+        <v>3.002739012046304</v>
       </c>
       <c r="E33" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F33" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>5.484001458551395</v>
+        <v>0.8911502370146017</v>
       </c>
       <c r="D34" t="n">
-        <v>14.39037599570072</v>
+        <v>2.338436099301366</v>
       </c>
       <c r="E34" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F34" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>9.968058224220632</v>
+        <v>1.619809461435853</v>
       </c>
       <c r="D35" t="n">
-        <v>12.32142708133916</v>
+        <v>2.002231900717614</v>
       </c>
       <c r="E35" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F35" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>8.761047472930954</v>
+        <v>1.42367021435128</v>
       </c>
       <c r="D36" t="n">
-        <v>4.247939828077495</v>
+        <v>0.6902902220625929</v>
       </c>
       <c r="E36" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F36" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>7.964925726738831</v>
+        <v>1.29430043059506</v>
       </c>
       <c r="D37" t="n">
-        <v>8.632882223399157</v>
+        <v>1.402843361302363</v>
       </c>
       <c r="E37" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F37" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>18.41496120712098</v>
+        <v>2.992431196157159</v>
       </c>
       <c r="D38" t="n">
-        <v>4.74623899506561</v>
+        <v>0.7712638366981617</v>
       </c>
       <c r="E38" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F38" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>10.42500481176934</v>
+        <v>1.694063281912518</v>
       </c>
       <c r="D39" t="n">
-        <v>4.664017635471849</v>
+        <v>0.7579028657641754</v>
       </c>
       <c r="E39" t="n">
-        <v>9.691011595314013</v>
+        <v>1.574789384238527</v>
       </c>
       <c r="F39" t="n">
-        <v>8.44840113096302</v>
+        <v>1.372865183781491</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
